--- a/02_Computer_Vision/Models(模型)/Semantic_Segmentation(语义分割)/图像分割模型对比表格.xlsx
+++ b/02_Computer_Vision/Models(模型)/Semantic_Segmentation(语义分割)/图像分割模型对比表格.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data\GitHubRepo\DeepLearning-notes\02_Computer_Vision\Models(模型)\Semantic_Segmentation(语义分割)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AfterDownload\Data\GithubRepository\DeepLearning-notes\02_Computer_Vision\Models(模型)\Semantic_Segmentation(语义分割)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30951C7-CF94-467B-B807-CE54F1DCFAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE661AC4-6D1F-456A-99AC-DD47F957713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>模型 (Model)</t>
   </si>
@@ -2283,6 +2283,316 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>分层Transformer、高效自注意力(Efficient Self-Attention)、混合前馈网络(Mix-FFN)、重叠块嵌入(Overlapped Patch Merging)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vision Transformer (ViT)、自注意力(Self-Attention)、Reassemble操作、多尺度特征融合、残差卷积单元(Residual Conv Unit)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构简洁高效，性能强大。因摒弃了位置编码，对不同分辨率输入的泛化能力和鲁棒性强。在同等计算量下达到SOTA性能。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有强大的全局上下文建模能力。打破了CNN在密集预测领域的传统范式，为ViT在下游任务的应用开辟了新方向。能灵活处理可变尺寸输入。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>化繁为简的典范</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SegFormer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深刻洞察到强大的编码器可以极大简化解码器的设计，其追求极致效率与性能平衡的设计哲学，使其成为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在分割领域的一个里程碑式的工作，证明了简洁架构的巨大潜力。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开创者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DPT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成功地将为分类设计的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ViT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>架构</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>翻译</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到了密集预测任务中，其设计的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reassemble</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模块优雅地解决了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Token</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到像素的转换难题，为后续大量基于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ViT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的分割</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深度估计模型铺平了道路。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaskFormer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将分割任务从传统的逐像素分类（Per-Pixel Classification）问题，重新定义为一个端到端的掩码分类（Mask Classification）问题。模型直接预测一组N个二值掩码，并为每个掩码预测一个对应的类别标签。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResNet, Swin Transformer等标准骨干网络。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩码分类(Mask Classification)、Transformer解码器、对象查询(Object Queries)、匈牙利算法(Hungarian Algorithm)二分图匹配、点积生成掩码、像素解码器(FPN-like)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>革命性工作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>。MaskFormer如同一座桥梁，成功地将Transformer和集合预测的思想从目标检测(DETR)引入到分割领域，开创了“掩码分类”这一全新范式。它不仅统一了三大分割任务，其核心思想更启发了后续一系列性能更强的模型(如Mask2Former)，深刻改变了现代分割模型的设计理念。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 架构统一，可同时处理多种分割任务。2. 输出允许掩码重叠（使用Sigmoid），天然适合实例分割。3. 性能强大，尤其在使用强力骨干网络时能达到SOTA水平。4. 训练过程比传统分割模型复杂，需采用集合损失函数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">1. </t>
     </r>
@@ -2357,21 +2667,31 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF333333"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <color rgb="FF333333"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Reassemble</t>
     </r>
     <r>
@@ -2444,6 +2764,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FFA7A7A7"/>
         <rFont val="等线"/>
@@ -2454,6 +2775,7 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <color rgb="FF333333"/>
         <rFont val="Arial"/>
@@ -2513,37 +2835,1051 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>分层Transformer、高效自注意力(Efficient Self-Attention)、混合前馈网络(Mix-FFN)、重叠块嵌入(Overlapped Patch Merging)。</t>
+    <r>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>范式转变</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>首次将分割视为一个“集合预测”问题，预测</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>掩码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对，摆脱了逐像素分类的束缚。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> 统一框架</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提出了一个对语义、实例和全景分割任务通用的统一架构，极大简化了模型设计。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> 基于查询的分割</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>借鉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>DETR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解码器和可学习的对象查询（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Object Queries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）来生成代表不同分割区域的嵌入。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Vision Transformer (ViT)、自注意力(Self-Attention)、Reassemble操作、多尺度特征融合、残差卷积单元(Residual Conv Unit)。</t>
+    <r>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>像素解码器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pixel Decoder)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: FPN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结构，生成高分辨率的逐像素嵌入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(E</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>pixel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">。                                                                           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解码器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Transformer Decoder)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>接收图像特征和对象查询，生成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个“每段嵌入”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Q</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>seg_emb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">。                                                                            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分割模块</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Segmentation Module)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将每段嵌入解码为类别和掩码。最终掩码由掩码嵌入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(E</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>mask</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>和像素嵌入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(E</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>pixel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的点积生成。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结构简洁高效，性能强大。因摒弃了位置编码，对不同分辨率输入的泛化能力和鲁棒性强。在同等计算量下达到SOTA性能。</t>
+    <t>Mask2Former</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>拥有强大的全局上下文建模能力。打破了CNN在密集预测领域的传统范式，为ViT在下游任务的应用开辟了新方向。能灵活处理可变尺寸输入。</t>
+    <t>在 MaskFormer 的“掩码分类”思想基础上，通过引入一个带有**掩码注意力(Masked Attention)**的全新 Transformer 解码器，极大地提升了分割任务的性能和训练效率，成为一个更强大、更高效的通用分割框架。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>化繁为简的典范</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>掩码注意力(Masked Attention)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 核心创新。将交叉注意力计算限制在预测的前景区域内，显著减少了计算量，加速了模型收敛，并提升了对局部特征的关注度。&lt;br&gt;2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>优化的Transformer解码器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 对解码器结构进行三点改进：① 交换注意力顺序（先交叉后自注），② 使用可学习的对象查询，③ 移除Dropout层。&lt;br&gt;3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>高效多尺度策略</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 循环地将像素解码器输出的不同分辨率特征图送入Transformer解码器的不同层，有效平衡了对小物体检测的性能和计算成本。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩码注意力(Masked Attention)、掩码分类(Mask Classification)、像素解码器(Pixel Decoder)、多尺度特征、可学习的对象查询、匈牙利算法、点采样损失计算(Point Sampling)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>像素解码器</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Pixel Decoder): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>采用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>FPN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>变体，生成用于最终掩码预测的高分辨率逐像素嵌入，并为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提供多尺度特征金字塔。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transformer</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解码器</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Transformer Decoder): </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模型的创新核心。由多个堆叠的解码器层组成，每一层都通过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>掩码注意力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、自注意力和</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>FFN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>来迭代地优化对象查询。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>性能卓越</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在语义、实例和全景分割三大任务上均达到了当时的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>SOTA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水平。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> 高效收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>由于掩码注意力的引入，相比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>MaskFormer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>训练速度更快，收敛所需周期更少。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t> 通用且强大</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单一模型即可胜任所有分割任务，无需针对特定任务进行结构修改。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MaskFormer的完美进化体</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
@@ -2553,237 +3889,21 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SegFormer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>深刻洞察到强大的编码器可以极大简化解码器的设计，其追求极致效率与性能平衡的设计哲学，使其成为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transformer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在分割领域的一个里程碑式的工作，证明了简洁架构的巨大潜力。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>开创者</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DPT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>成功地将为分类设计的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ViT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>架构</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>翻译</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到了密集预测任务中，其设计的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reassemble</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Fusion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模块优雅地解决了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Token</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到像素的转换难题，为后续大量基于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ViT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>的分割</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>深度估计模型铺平了道路。</t>
+        <color rgb="FF1F2328"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mask2Former</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>通过引入设计精巧的“掩码注意力”，精准地解决了前代模型中全局注意力的效率瓶颈，使得“掩码分类”这一范式变得前所未有的高效和强大。它不仅在性能上树立了新的标杆，也为后续的通用视觉模型设计提供了宝贵的实践经验，是分割领域发展史上的又一个里程碑。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2792,7 +3912,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2900,25 +4020,41 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFA7A7A7"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8F8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2948,37 +4084,121 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3254,341 +4474,434 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="47.625" customWidth="1"/>
-    <col min="5" max="5" width="25.375" customWidth="1"/>
-    <col min="6" max="6" width="33.625" customWidth="1"/>
-    <col min="7" max="7" width="26.25" customWidth="1"/>
-    <col min="8" max="8" width="25.25" customWidth="1"/>
-    <col min="9" max="9" width="38.375" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="47.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="34.5546875" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" customWidth="1"/>
+    <col min="8" max="8" width="25.21875" customWidth="1"/>
+    <col min="9" max="9" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="4">
         <v>2015</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="4">
         <v>2015</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>2018</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:9" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>2017</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>2019</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="99" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:9" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="4">
         <v>2023</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:9" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="4">
         <v>2018</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="131.44999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:9" ht="131.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>2021</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="82.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>2021</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2021</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H11" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I11" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="115.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="6">
+    <row r="12" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="4">
         <v>2021</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>88</v>
+      <c r="C12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="152.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2022</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:I12">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13:I13">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(), 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
